--- a/src/conf/case_analysis.xlsx
+++ b/src/conf/case_analysis.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26860" windowHeight="11060" tabRatio="962" firstSheet="5" activeTab="9"/>
+    <workbookView windowWidth="27660" windowHeight="11120" tabRatio="962" firstSheet="5" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="sector_3_turns_screening" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="114">
   <si>
     <t>Initial KG
 (Expansion by the LLM Ensemble)</t>
@@ -222,9 +222,6 @@
   </si>
   <si>
     <t>c014</t>
-  </si>
-  <si>
-    <t>c015</t>
   </si>
   <si>
     <t>c016</t>
@@ -2405,139 +2402,139 @@
     <row r="17" ht="17" spans="2:12">
       <c r="B17" s="18" t="str">
         <f>sector_data!A15</f>
-        <v>c015</v>
+        <v>c016</v>
       </c>
       <c r="C17" s="19">
         <f>SUM(sector_data!B15,sector_data!D15)</f>
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="D17" s="19">
         <f>sector_data!C15+sector_data!E15</f>
-        <v>147</v>
+        <v>100</v>
       </c>
       <c r="E17" s="23">
         <f>sector_data!F15</f>
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="F17" s="23">
         <f>sector_data!G15</f>
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="G17" s="23">
         <f>sector_data!H15</f>
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="H17" s="23">
         <f>sector_data!I15</f>
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="I17" s="23">
         <f>sector_data!J15</f>
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="J17" s="23">
         <f>sector_data!K15</f>
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="K17" s="24">
         <f>sector_data!L15</f>
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="L17" s="24">
         <f>sector_data!M15</f>
-        <v>0.81</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="18" ht="17" spans="2:12">
       <c r="B18" s="18" t="str">
         <f>sector_data!A16</f>
-        <v>c016</v>
+        <v>c017</v>
       </c>
       <c r="C18" s="19">
         <f>SUM(sector_data!B16,sector_data!D16)</f>
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D18" s="19">
         <f>sector_data!C16+sector_data!E16</f>
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="E18" s="23">
         <f>sector_data!F16</f>
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F18" s="23">
         <f>sector_data!G16</f>
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="G18" s="23">
         <f>sector_data!H16</f>
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H18" s="23">
         <f>sector_data!I16</f>
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="I18" s="23">
         <f>sector_data!J16</f>
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J18" s="23">
         <f>sector_data!K16</f>
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K18" s="24">
         <f>sector_data!L16</f>
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="L18" s="24">
         <f>sector_data!M16</f>
-        <v>0.87</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="19" ht="17" spans="2:12">
-      <c r="B19" s="18" t="str">
+      <c r="B19" s="18">
         <f>sector_data!A17</f>
-        <v>c017</v>
+        <v>0</v>
       </c>
       <c r="C19" s="19">
         <f>SUM(sector_data!B17,sector_data!D17)</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D19" s="19">
         <f>sector_data!C17+sector_data!E17</f>
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="E19" s="23">
         <f>sector_data!F17</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F19" s="23">
         <f>sector_data!G17</f>
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="G19" s="23">
         <f>sector_data!H17</f>
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H19" s="23">
         <f>sector_data!I17</f>
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="I19" s="23">
         <f>sector_data!J17</f>
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="J19" s="23">
         <f>sector_data!K17</f>
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="K19" s="24">
         <f>sector_data!L17</f>
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="L19" s="24">
         <f>sector_data!M17</f>
-        <v>0.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:12">
@@ -2924,8 +2921,8 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="22.0078125" customWidth="1"/>
     <col min="2" max="2" width="16.015625" customWidth="1"/>
@@ -2933,26 +2930,26 @@
     <col min="4" max="4" width="13.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" spans="1:4">
+    <row r="1" ht="34" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" ht="17" spans="1:5">
+      <c r="A2" s="2" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="2" ht="17" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="B2" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3">
         <v>22</v>
@@ -2961,13 +2958,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" ht="17" spans="1:4">
+    <row r="3" ht="17" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B3" s="4">
-        <f>sector_3_turns_screening_s001!B19</f>
-        <v>1376</v>
+        <f>sector_3_turns_screening_s001!B18</f>
+        <v>1290</v>
       </c>
       <c r="C3" s="4">
         <f>sector_3_turns_screening_s002!B25</f>
@@ -2977,14 +2974,18 @@
         <f>sector_3_turns_screening_s003!B27</f>
         <v>1845</v>
       </c>
-    </row>
-    <row r="4" ht="17" spans="1:4">
+      <c r="E3">
+        <f t="shared" ref="E3:E7" si="0">SUM(B3:D3)</f>
+        <v>4673</v>
+      </c>
+    </row>
+    <row r="4" ht="17" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B4" s="4">
-        <f>sector_3_turns_screening_s001!H19</f>
-        <v>1086</v>
+        <f>sector_3_turns_screening_s001!H18</f>
+        <v>1018</v>
       </c>
       <c r="C4" s="4">
         <f>sector_3_turns_screening_s002!H25</f>
@@ -2994,14 +2995,18 @@
         <f>sector_3_turns_screening_s003!H27</f>
         <v>1440</v>
       </c>
-    </row>
-    <row r="5" ht="17" spans="1:4">
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>3690</v>
+      </c>
+    </row>
+    <row r="5" ht="17" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B5" s="5">
-        <f>sector_3_turns_screening_s001!J19</f>
-        <v>0.789244186046512</v>
+        <f>sector_3_turns_screening_s001!J18</f>
+        <v>0.789147286821705</v>
       </c>
       <c r="C5" s="5">
         <f>sector_3_turns_screening_s002!J25</f>
@@ -3012,13 +3017,13 @@
         <v>0.780487804878049</v>
       </c>
     </row>
-    <row r="6" ht="17" spans="1:4">
+    <row r="6" ht="17" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B6" s="4">
-        <f>sector_3_turns_screening_s001!C19</f>
-        <v>2318</v>
+        <f>sector_3_turns_screening_s001!C18</f>
+        <v>2171</v>
       </c>
       <c r="C6" s="4">
         <f>sector_3_turns_screening_s002!C25</f>
@@ -3028,14 +3033,18 @@
         <f>sector_3_turns_screening_s003!C27</f>
         <v>3284</v>
       </c>
-    </row>
-    <row r="7" ht="17" spans="1:4">
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>8106</v>
+      </c>
+    </row>
+    <row r="7" ht="17" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B7" s="4">
-        <f>sector_3_turns_screening_s001!I19</f>
-        <v>1751</v>
+        <f>sector_3_turns_screening_s001!I18</f>
+        <v>1632</v>
       </c>
       <c r="C7" s="4">
         <f>sector_3_turns_screening_s002!I25</f>
@@ -3045,14 +3054,18 @@
         <f>sector_3_turns_screening_s003!I27</f>
         <v>2290</v>
       </c>
-    </row>
-    <row r="8" ht="17" spans="1:4">
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>5822</v>
+      </c>
+    </row>
+    <row r="8" ht="17" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B8" s="5">
-        <f>sector_3_turns_screening_s001!K19</f>
-        <v>0.755392579810181</v>
+        <f>sector_3_turns_screening_s001!K18</f>
+        <v>0.751727314601566</v>
       </c>
       <c r="C8" s="5">
         <f>sector_3_turns_screening_s002!K25</f>
@@ -3063,9 +3076,9 @@
         <v>0.697320341047503</v>
       </c>
     </row>
-    <row r="9" ht="34" spans="1:4">
+    <row r="9" ht="34" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B9" s="3">
         <v>1.41</v>
@@ -3079,9 +3092,9 @@
         <v>1.34541666666667</v>
       </c>
     </row>
-    <row r="10" ht="34" spans="1:4">
+    <row r="10" ht="34" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B10" s="3">
         <v>1.28</v>
@@ -3095,12 +3108,12 @@
         <v>1.18125</v>
       </c>
     </row>
-    <row r="11" ht="34" spans="1:4">
+    <row r="11" ht="34" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B11" s="5">
-        <v>0.825</v>
+        <v>0.8227</v>
       </c>
       <c r="C11" s="5">
         <f>sector_DST_s002!J24</f>
@@ -3111,12 +3124,12 @@
         <v>0.807083333333333</v>
       </c>
     </row>
-    <row r="12" ht="34" spans="1:4">
+    <row r="12" ht="34" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B12" s="3" t="str">
-        <f>sector_DST_s001!J19</f>
+        <f>sector_DST_s001!J18</f>
         <v>66.00%-100.00%</v>
       </c>
       <c r="C12" s="3" t="str">
@@ -3128,9 +3141,9 @@
         <v>59.00%-93.00%</v>
       </c>
     </row>
-    <row r="13" ht="17" spans="1:4">
+    <row r="13" ht="17" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B13" s="7">
         <v>1</v>
@@ -3742,127 +3755,127 @@
     <row r="16" ht="17" spans="2:11">
       <c r="B16" s="18" t="str">
         <f>sector_data!A15</f>
-        <v>c015</v>
+        <v>c016</v>
       </c>
       <c r="C16" s="19">
         <f>sector_data!B15</f>
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="D16" s="19">
         <f>sector_data!D15</f>
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E16" s="19">
         <f>sector_data!C15</f>
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="F16" s="19">
         <f>sector_data!E15</f>
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="G16" s="19">
         <f>sector_data!J15</f>
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="H16" s="19">
         <f>sector_data!K15</f>
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="I16" s="19">
         <f>sector_data!N15</f>
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="J16" s="19">
         <f>sector_data!O15</f>
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="K16" s="20">
         <f>sector_data!P15</f>
-        <v>0.86</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="17" ht="17" spans="2:11">
       <c r="B17" s="18" t="str">
         <f>sector_data!A16</f>
-        <v>c016</v>
+        <v>c017</v>
       </c>
       <c r="C17" s="19">
         <f>sector_data!B16</f>
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D17" s="19">
         <f>sector_data!D16</f>
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E17" s="19">
         <f>sector_data!C16</f>
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F17" s="19">
         <f>sector_data!E16</f>
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G17" s="19">
         <f>sector_data!J16</f>
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H17" s="19">
         <f>sector_data!K16</f>
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="I17" s="19">
         <f>sector_data!N16</f>
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="J17" s="19">
         <f>sector_data!O16</f>
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="K17" s="20">
         <f>sector_data!P16</f>
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="18" ht="17" spans="2:11">
-      <c r="B18" s="18" t="str">
+      <c r="B18" s="18">
         <f>sector_data!A17</f>
-        <v>c017</v>
+        <v>0</v>
       </c>
       <c r="C18" s="19">
         <f>sector_data!B17</f>
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D18" s="19">
         <f>sector_data!D17</f>
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E18" s="19">
         <f>sector_data!C17</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F18" s="19">
         <f>sector_data!E17</f>
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G18" s="19">
         <f>sector_data!J17</f>
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H18" s="19">
         <f>sector_data!K17</f>
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="I18" s="19">
         <f>sector_data!N17</f>
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="J18" s="19">
         <f>sector_data!O17</f>
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="K18" s="20">
         <f>sector_data!P17</f>
-        <v>0.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:11">
@@ -4214,7 +4227,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr defaultColWidth="8.4375" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="16384" width="8.4375" style="15"/>
@@ -4925,49 +4938,49 @@
         <v>45</v>
       </c>
       <c r="B15" s="15">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="C15" s="15">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="D15" s="15">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E15" s="15">
+        <v>70</v>
+      </c>
+      <c r="F15" s="15">
+        <v>63</v>
+      </c>
+      <c r="G15" s="15">
+        <v>100</v>
+      </c>
+      <c r="H15" s="15">
+        <v>59</v>
+      </c>
+      <c r="I15" s="15">
+        <v>87</v>
+      </c>
+      <c r="J15" s="15">
         <v>54</v>
       </c>
-      <c r="F15" s="15">
-        <v>86</v>
-      </c>
-      <c r="G15" s="15">
-        <v>146</v>
-      </c>
-      <c r="H15" s="15">
-        <v>83</v>
-      </c>
-      <c r="I15" s="15">
-        <v>121</v>
-      </c>
-      <c r="J15" s="15">
-        <v>68</v>
-      </c>
       <c r="K15" s="15">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="L15" s="15">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="M15" s="15">
-        <v>0.81</v>
+        <v>0.87</v>
       </c>
       <c r="N15" s="15">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="O15" s="15">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="P15" s="15">
-        <v>0.86</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="16" s="15" customFormat="1" spans="1:16">
@@ -4975,98 +4988,48 @@
         <v>46</v>
       </c>
       <c r="B16" s="15">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C16" s="15">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D16" s="15">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E16" s="15">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F16" s="15">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G16" s="15">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="H16" s="15">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I16" s="15">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="J16" s="15">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="K16" s="15">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="L16" s="15">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="M16" s="15">
-        <v>0.87</v>
+        <v>0.81</v>
       </c>
       <c r="N16" s="15">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="O16" s="15">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P16" s="15">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="17" s="15" customFormat="1" spans="1:16">
-      <c r="A17" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="15">
-        <v>29</v>
-      </c>
-      <c r="C17" s="15">
-        <v>40</v>
-      </c>
-      <c r="D17" s="15">
-        <v>31</v>
-      </c>
-      <c r="E17" s="15">
-        <v>72</v>
-      </c>
-      <c r="F17" s="15">
-        <v>60</v>
-      </c>
-      <c r="G17" s="15">
-        <v>112</v>
-      </c>
-      <c r="H17" s="15">
-        <v>57</v>
-      </c>
-      <c r="I17" s="15">
-        <v>93</v>
-      </c>
-      <c r="J17" s="15">
-        <v>49</v>
-      </c>
-      <c r="K17" s="15">
-        <v>91</v>
-      </c>
-      <c r="L17" s="15">
-        <v>0.82</v>
-      </c>
-      <c r="M17" s="15">
-        <v>0.81</v>
-      </c>
-      <c r="N17" s="15">
-        <v>1.58</v>
-      </c>
-      <c r="O17" s="15">
-        <v>1.26</v>
-      </c>
-      <c r="P17" s="15">
         <v>0.76</v>
       </c>
     </row>
@@ -5094,11 +5057,11 @@
         <v>8</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C1" s="11"/>
       <c r="D1" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E1" s="11"/>
       <c r="F1" s="8" t="s">
@@ -5119,7 +5082,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B2">
         <v>37</v>
@@ -5151,7 +5114,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B3">
         <v>33</v>
@@ -5183,7 +5146,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B4">
         <v>17</v>
@@ -5215,7 +5178,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B5">
         <v>32</v>
@@ -5247,7 +5210,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B6">
         <v>32</v>
@@ -5279,7 +5242,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B7">
         <v>58</v>
@@ -5311,7 +5274,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B8">
         <v>70</v>
@@ -5343,7 +5306,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B9">
         <v>28</v>
@@ -5375,7 +5338,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B10">
         <v>68</v>
@@ -5407,7 +5370,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B11">
         <v>45</v>
@@ -5439,7 +5402,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B12">
         <v>22</v>
@@ -5471,7 +5434,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B13">
         <v>37</v>
@@ -5503,7 +5466,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B14">
         <v>21</v>
@@ -5535,7 +5498,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B15">
         <v>59</v>
@@ -5567,7 +5530,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B16">
         <v>47</v>
@@ -5599,7 +5562,7 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B17">
         <v>53</v>
@@ -5631,7 +5594,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B18">
         <v>36</v>
@@ -5663,7 +5626,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B19">
         <v>64</v>
@@ -5695,7 +5658,7 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B20">
         <v>45</v>
@@ -5727,7 +5690,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B21">
         <v>40</v>
@@ -5759,7 +5722,7 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B22">
         <v>31</v>
@@ -5791,7 +5754,7 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B23">
         <v>25</v>
@@ -5823,7 +5786,7 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B24">
         <v>37</v>
@@ -5855,7 +5818,7 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B25">
         <v>42</v>
@@ -5984,7 +5947,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B3">
         <v>73</v>
@@ -6019,7 +5982,7 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4">
         <v>59</v>
@@ -6054,7 +6017,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B5">
         <v>52</v>
@@ -6089,7 +6052,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6">
         <v>71</v>
@@ -6124,7 +6087,7 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B7">
         <v>77</v>
@@ -6159,7 +6122,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B8">
         <v>89</v>
@@ -6194,7 +6157,7 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B9">
         <v>103</v>
@@ -6229,7 +6192,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B10">
         <v>63</v>
@@ -6264,7 +6227,7 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B11">
         <v>109</v>
@@ -6299,7 +6262,7 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B12">
         <v>77</v>
@@ -6334,7 +6297,7 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13">
         <v>44</v>
@@ -6369,7 +6332,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B14">
         <v>75</v>
@@ -6404,7 +6367,7 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B15">
         <v>68</v>
@@ -6439,7 +6402,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B16">
         <v>108</v>
@@ -6474,7 +6437,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B17">
         <v>73</v>
@@ -6509,7 +6472,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B18">
         <v>125</v>
@@ -6544,7 +6507,7 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B19">
         <v>57</v>
@@ -6579,7 +6542,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B20">
         <v>97</v>
@@ -6614,7 +6577,7 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B21">
         <v>81</v>
@@ -6649,7 +6612,7 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B22">
         <v>68</v>
@@ -6684,7 +6647,7 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B23">
         <v>73</v>
@@ -6719,7 +6682,7 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B24">
         <v>56</v>
@@ -6754,7 +6717,7 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B25">
         <v>68</v>
@@ -6789,7 +6752,7 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B26">
         <v>79</v>
@@ -6824,7 +6787,7 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B27">
         <f>SUM(B3:B26)</f>
@@ -6851,7 +6814,7 @@
         <v>0.697320341047503</v>
       </c>
       <c r="L27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -6885,11 +6848,11 @@
         <v>8</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C1" s="11"/>
       <c r="D1" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E1" s="11"/>
       <c r="F1" s="8" t="s">
@@ -6910,7 +6873,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2">
         <v>34</v>
@@ -6942,7 +6905,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B3">
         <v>39</v>
@@ -6974,7 +6937,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B4">
         <v>28</v>
@@ -7006,7 +6969,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B5">
         <v>27</v>
@@ -7038,7 +7001,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B6">
         <v>50</v>
@@ -7070,7 +7033,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B7">
         <v>14</v>
@@ -7102,7 +7065,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B8">
         <v>48</v>
@@ -7134,7 +7097,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B9">
         <v>63</v>
@@ -7166,7 +7129,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B10">
         <v>51</v>
@@ -7198,7 +7161,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B11">
         <v>15</v>
@@ -7230,7 +7193,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12">
         <v>55</v>
@@ -7262,7 +7225,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B13">
         <v>42</v>
@@ -7294,7 +7257,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B14">
         <v>20</v>
@@ -7326,7 +7289,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B15">
         <v>25</v>
@@ -7358,7 +7321,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B16">
         <v>36</v>
@@ -7390,7 +7353,7 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B17">
         <v>27</v>
@@ -7422,7 +7385,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B18">
         <v>26</v>
@@ -7454,7 +7417,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B19">
         <v>38</v>
@@ -7486,7 +7449,7 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B20">
         <v>16</v>
@@ -7518,7 +7481,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B21">
         <v>40</v>
@@ -7550,7 +7513,7 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B22">
         <v>32</v>
@@ -7582,7 +7545,7 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B23">
         <v>22</v>
@@ -7711,7 +7674,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B3">
         <v>70</v>
@@ -7746,7 +7709,7 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B4">
         <v>74</v>
@@ -7781,7 +7744,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B5">
         <v>65</v>
@@ -7816,7 +7779,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B6">
         <v>61</v>
@@ -7851,7 +7814,7 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B7">
         <v>95</v>
@@ -7886,7 +7849,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B8">
         <v>49</v>
@@ -7921,7 +7884,7 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B9">
         <v>87</v>
@@ -7956,7 +7919,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B10">
         <v>128</v>
@@ -7991,7 +7954,7 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B11">
         <v>76</v>
@@ -8026,7 +7989,7 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B12">
         <v>47</v>
@@ -8061,7 +8024,7 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B13">
         <v>94</v>
@@ -8096,7 +8059,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B14">
         <v>72</v>
@@ -8131,7 +8094,7 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B15">
         <v>41</v>
@@ -8166,7 +8129,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B16">
         <v>41</v>
@@ -8201,7 +8164,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B17">
         <v>89</v>
@@ -8236,7 +8199,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B18">
         <v>77</v>
@@ -8271,7 +8234,7 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B19">
         <v>60</v>
@@ -8306,7 +8269,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B20">
         <v>61</v>
@@ -8341,7 +8304,7 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B21">
         <v>47</v>
@@ -8376,7 +8339,7 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B22">
         <v>67</v>
@@ -8411,7 +8374,7 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B23">
         <v>77</v>
@@ -8446,7 +8409,7 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B24">
         <v>60</v>
@@ -8481,7 +8444,7 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B25">
         <f>SUM(B3:B24)</f>
@@ -8508,7 +8471,7 @@
         <v>0.716710675216899</v>
       </c>
       <c r="L25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -8527,9 +8490,11 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.234375" customWidth="1"/>
     <col min="8" max="8" width="11.0703125" customWidth="1"/>
     <col min="9" max="9" width="10.8046875" customWidth="1"/>
     <col min="10" max="10" width="16.3125" customWidth="1"/>
@@ -8540,11 +8505,11 @@
         <v>8</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C1" s="11"/>
       <c r="D1" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E1" s="11"/>
       <c r="F1" s="8" t="s">
@@ -8984,31 +8949,31 @@
         <v>45</v>
       </c>
       <c r="B15">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="C15">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D15">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="E15">
+        <v>70</v>
+      </c>
+      <c r="F15">
         <v>54</v>
       </c>
-      <c r="F15">
-        <v>68</v>
-      </c>
       <c r="G15">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="H15" s="12">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="I15" s="12">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="J15" s="13">
-        <v>0.86</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -9016,82 +8981,66 @@
         <v>46</v>
       </c>
       <c r="B16">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C16">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D16">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E16">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F16">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G16">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H16" s="12">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="I16" s="12">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="J16" s="13">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" t="s">
-        <v>47</v>
-      </c>
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10">
       <c r="B17">
-        <v>29</v>
+        <f t="shared" ref="B17:F17" si="0">SUM(B2:B16)</f>
+        <v>666</v>
       </c>
       <c r="C17">
-        <v>31</v>
+        <f t="shared" si="0"/>
+        <v>624</v>
       </c>
       <c r="D17">
-        <v>40</v>
+        <f t="shared" si="0"/>
+        <v>1015</v>
       </c>
       <c r="E17">
-        <v>72</v>
-      </c>
-      <c r="F17">
-        <v>49</v>
-      </c>
-      <c r="G17">
-        <v>91</v>
+        <f t="shared" si="0"/>
+        <v>1156</v>
       </c>
       <c r="H17" s="12">
-        <v>1.58</v>
+        <f>AVERAGE(H2:H16)</f>
+        <v>1.39466666666667</v>
       </c>
       <c r="I17" s="12">
-        <v>1.26</v>
+        <f>AVERAGE(I2:I16)</f>
+        <v>1.278</v>
       </c>
       <c r="J17" s="13">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="H18" s="12">
-        <f>AVERAGE(H2:H17)</f>
-        <v>1.40625</v>
-      </c>
-      <c r="I18" s="12">
-        <f>AVERAGE(I2:I17)</f>
-        <v>1.278125</v>
-      </c>
-      <c r="J18" s="13">
-        <f>AVERAGE(J2:J17)</f>
-        <v>0.825</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="J19" t="str">
-        <f>TEXT(MIN(J2:J18),"0.00%")&amp;"-"&amp;TEXT(MAX(J2:J18),"0.00%")</f>
+        <f>AVERAGE(J2:J16)</f>
+        <v>0.822666666666667</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10">
+      <c r="J18" t="str">
+        <f>TEXT(MIN(J2:J17),"0.00%")&amp;"-"&amp;TEXT(MAX(J2:J17),"0.00%")</f>
         <v>66.00%-100.00%</v>
       </c>
     </row>
@@ -9108,7 +9057,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" s="8" customFormat="1" ht="63" customHeight="1" spans="1:11">
@@ -9629,34 +9578,34 @@
         <v>45</v>
       </c>
       <c r="B16" s="9">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="C16" s="9">
-        <v>147</v>
+        <v>100</v>
       </c>
       <c r="D16" s="9">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="E16" s="9">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="F16" s="9">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="G16" s="9">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="H16" s="9">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="I16" s="9">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="J16" s="10">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="K16" s="10">
-        <v>0.81</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -9664,105 +9613,70 @@
         <v>46</v>
       </c>
       <c r="B17" s="9">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C17" s="9">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="D17" s="9">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E17" s="9">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="F17" s="9">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G17" s="9">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="H17" s="9">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I17" s="9">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J17" s="10">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="K17" s="10">
-        <v>0.87</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="9" t="s">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="B18" s="9">
-        <v>60</v>
+        <f>SUM(B3:B17)</f>
+        <v>1290</v>
       </c>
       <c r="C18" s="9">
-        <v>112</v>
-      </c>
-      <c r="D18" s="9">
-        <v>60</v>
-      </c>
-      <c r="E18" s="9">
-        <v>112</v>
-      </c>
-      <c r="F18" s="9">
-        <v>57</v>
-      </c>
-      <c r="G18" s="9">
-        <v>93</v>
-      </c>
+        <f>SUM(C3:C17)</f>
+        <v>2171</v>
+      </c>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
       <c r="H18" s="9">
-        <v>49</v>
+        <f>SUM(H3:H17)</f>
+        <v>1018</v>
       </c>
       <c r="I18" s="9">
-        <v>91</v>
+        <f>SUM(I3:I17)</f>
+        <v>1632</v>
       </c>
       <c r="J18" s="10">
-        <v>0.82</v>
+        <f>H18/B18</f>
+        <v>0.789147286821705</v>
       </c>
       <c r="K18" s="10">
-        <v>0.81</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B19" s="9">
-        <f>SUM(B3:B18)</f>
-        <v>1376</v>
-      </c>
-      <c r="C19" s="9">
-        <f>SUM(C3:C18)</f>
-        <v>2318</v>
-      </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9">
-        <f t="shared" ref="H19:K19" si="0">SUM(H3:H18)</f>
-        <v>1086</v>
-      </c>
-      <c r="I19" s="9">
-        <f t="shared" si="0"/>
-        <v>1751</v>
-      </c>
-      <c r="J19" s="10">
-        <f>H19/B19</f>
-        <v>0.789244186046512</v>
-      </c>
-      <c r="K19" s="10">
-        <f>I19/C19</f>
-        <v>0.755392579810181</v>
-      </c>
-      <c r="L19" t="s">
-        <v>75</v>
+        <f>I18/C18</f>
+        <v>0.751727314601566</v>
+      </c>
+      <c r="L18" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
